--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99CE27EB-4428-4BCB-82FD-78E2A8D512BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66FC99F7-A46B-459E-9E99-5B125C538112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{9A65E36C-6644-4631-90F3-512D03703D5D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{CE6C8F3A-5250-4DB6-9DEE-D2CC61123543}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A75BE859-EAB0-486F-9A23-2B1D8C384184}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689DB5EE-94E0-4289-8A19-D66EB6321CB6}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA373A89-FFCD-49A1-8D44-A7AFF9CF70C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DBE7E7-B8DE-4DFF-B1AE-F0E8ACD3C95B}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3928FBD-CA3E-4F90-A0D5-0E502E69D074}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0C66BA-2963-4CB7-BE0E-3AF23BBFCA95}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -50109,7 +50109,7 @@
         <v>14</v>
       </c>
       <c r="R368" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S368" t="s">
         <v>897</v>
@@ -50168,7 +50168,7 @@
         <v>14</v>
       </c>
       <c r="R369" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S369" t="s">
         <v>897</v>
@@ -50463,7 +50463,7 @@
         <v>14</v>
       </c>
       <c r="R374" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S374" t="s">
         <v>897</v>
@@ -50522,7 +50522,7 @@
         <v>14</v>
       </c>
       <c r="R375" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S375" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -67166,7 +67166,7 @@
         <v>14</v>
       </c>
       <c r="R663" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S663" t="s">
         <v>897</v>
@@ -67216,7 +67216,7 @@
         <v>14</v>
       </c>
       <c r="R664" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S664" t="s">
         <v>897</v>
@@ -68361,7 +68361,7 @@
         <v>14</v>
       </c>
       <c r="R686" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S686" t="s">
         <v>897</v>
@@ -68411,7 +68411,7 @@
         <v>14</v>
       </c>
       <c r="R687" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S687" t="s">
         <v>897</v>
@@ -68861,7 +68861,7 @@
         <v>14</v>
       </c>
       <c r="R696" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S696" t="s">
         <v>897</v>
@@ -68911,7 +68911,7 @@
         <v>14</v>
       </c>
       <c r="R697" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S697" t="s">
         <v>897</v>
@@ -69061,7 +69061,7 @@
         <v>14</v>
       </c>
       <c r="R700" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S700" t="s">
         <v>897</v>
@@ -69111,7 +69111,7 @@
         <v>14</v>
       </c>
       <c r="R701" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S701" t="s">
         <v>897</v>
@@ -71848,7 +71848,7 @@
         <v>33</v>
       </c>
       <c r="M775">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="776" spans="2:13" x14ac:dyDescent="0.25">
@@ -71877,7 +71877,7 @@
         <v>33</v>
       </c>
       <c r="M776">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="777" spans="2:13" x14ac:dyDescent="0.25">
@@ -71906,7 +71906,7 @@
         <v>33</v>
       </c>
       <c r="M777">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="778" spans="2:13" x14ac:dyDescent="0.25">
@@ -83449,7 +83449,7 @@
         <v>33</v>
       </c>
       <c r="M1081">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1082" spans="2:13" x14ac:dyDescent="0.25">
@@ -83478,7 +83478,7 @@
         <v>33</v>
       </c>
       <c r="M1082">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1083" spans="2:13" x14ac:dyDescent="0.25">
@@ -83507,7 +83507,7 @@
         <v>33</v>
       </c>
       <c r="M1083">
-        <v>0.41074925609602891</v>
+        <v>0.4107492560960288</v>
       </c>
     </row>
     <row r="1084" spans="2:13" x14ac:dyDescent="0.25">
@@ -83840,7 +83840,7 @@
         <v>33</v>
       </c>
       <c r="M1092">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1093" spans="2:13" x14ac:dyDescent="0.25">
@@ -83869,7 +83869,7 @@
         <v>33</v>
       </c>
       <c r="M1093">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1094" spans="2:13" x14ac:dyDescent="0.25">
@@ -83898,7 +83898,7 @@
         <v>33</v>
       </c>
       <c r="M1094">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1095" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C23E92-20F6-4536-92DD-A442EAF84B03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5BA4C5-6A8C-4705-97B0-D4B961311166}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66FC99F7-A46B-459E-9E99-5B125C538112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C89AE9E8-A566-4B77-872C-2F8291EEEB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{CE6C8F3A-5250-4DB6-9DEE-D2CC61123543}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{FB7F7012-F599-4192-BE4A-100ED6B1AD0A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689DB5EE-94E0-4289-8A19-D66EB6321CB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D9CEA7-E2A5-4ACF-92E5-037DD529CB2C}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DBE7E7-B8DE-4DFF-B1AE-F0E8ACD3C95B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA32F76-05C5-4C58-B70E-952FC1CF0147}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0C66BA-2963-4CB7-BE0E-3AF23BBFCA95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3277808B-E8CE-46B5-BB70-C53E3AD3653C}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -65660,7 +65660,7 @@
         <v>14</v>
       </c>
       <c r="R636" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S636" t="s">
         <v>897</v>
@@ -65716,7 +65716,7 @@
         <v>14</v>
       </c>
       <c r="R637" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S637" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -68361,7 +68361,7 @@
         <v>14</v>
       </c>
       <c r="R686" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S686" t="s">
         <v>897</v>
@@ -68411,7 +68411,7 @@
         <v>14</v>
       </c>
       <c r="R687" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S687" t="s">
         <v>897</v>
@@ -68861,7 +68861,7 @@
         <v>14</v>
       </c>
       <c r="R696" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S696" t="s">
         <v>897</v>
@@ -68911,7 +68911,7 @@
         <v>14</v>
       </c>
       <c r="R697" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S697" t="s">
         <v>897</v>
@@ -68961,7 +68961,7 @@
         <v>14</v>
       </c>
       <c r="R698" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S698" t="s">
         <v>897</v>
@@ -69011,7 +69011,7 @@
         <v>14</v>
       </c>
       <c r="R699" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S699" t="s">
         <v>897</v>
@@ -71848,7 +71848,7 @@
         <v>33</v>
       </c>
       <c r="M775">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="776" spans="2:13" x14ac:dyDescent="0.25">
@@ -71877,7 +71877,7 @@
         <v>33</v>
       </c>
       <c r="M776">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="777" spans="2:13" x14ac:dyDescent="0.25">
@@ -71906,7 +71906,7 @@
         <v>33</v>
       </c>
       <c r="M777">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="778" spans="2:13" x14ac:dyDescent="0.25">
@@ -83840,7 +83840,7 @@
         <v>33</v>
       </c>
       <c r="M1092">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1093" spans="2:13" x14ac:dyDescent="0.25">
@@ -83869,7 +83869,7 @@
         <v>33</v>
       </c>
       <c r="M1093">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1094" spans="2:13" x14ac:dyDescent="0.25">
@@ -83898,7 +83898,7 @@
         <v>33</v>
       </c>
       <c r="M1094">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1095" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5BA4C5-6A8C-4705-97B0-D4B961311166}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8314EFFA-E318-4F31-BE1B-3F3417261222}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C89AE9E8-A566-4B77-872C-2F8291EEEB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEF2FD8E-F80A-40EE-A006-EFAA52CFEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{FB7F7012-F599-4192-BE4A-100ED6B1AD0A}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{59CF439D-C559-4B4A-B75E-B52EF0A99577}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D9CEA7-E2A5-4ACF-92E5-037DD529CB2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E299A37C-20B6-4383-98AC-D1FD9DB1E817}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA32F76-05C5-4C58-B70E-952FC1CF0147}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0068B1A7-124C-42D7-A45A-FC597F7F2F51}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3277808B-E8CE-46B5-BB70-C53E3AD3653C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9D909-A04F-4FD1-A0A6-CEACBAC939CA}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -65660,7 +65660,7 @@
         <v>14</v>
       </c>
       <c r="R636" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S636" t="s">
         <v>897</v>
@@ -65716,7 +65716,7 @@
         <v>14</v>
       </c>
       <c r="R637" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S637" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -68461,7 +68461,7 @@
         <v>14</v>
       </c>
       <c r="R688" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S688" t="s">
         <v>897</v>
@@ -68511,7 +68511,7 @@
         <v>14</v>
       </c>
       <c r="R689" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S689" t="s">
         <v>897</v>
@@ -71848,7 +71848,7 @@
         <v>33</v>
       </c>
       <c r="M775">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="776" spans="2:13" x14ac:dyDescent="0.25">
@@ -71877,7 +71877,7 @@
         <v>33</v>
       </c>
       <c r="M776">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="777" spans="2:13" x14ac:dyDescent="0.25">
@@ -71906,7 +71906,7 @@
         <v>33</v>
       </c>
       <c r="M777">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="778" spans="2:13" x14ac:dyDescent="0.25">
@@ -83840,7 +83840,7 @@
         <v>33</v>
       </c>
       <c r="M1092">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1093" spans="2:13" x14ac:dyDescent="0.25">
@@ -83869,7 +83869,7 @@
         <v>33</v>
       </c>
       <c r="M1093">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1094" spans="2:13" x14ac:dyDescent="0.25">
@@ -83898,7 +83898,7 @@
         <v>33</v>
       </c>
       <c r="M1094">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1095" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8314EFFA-E318-4F31-BE1B-3F3417261222}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF158A-C6C6-4D01-8ED6-802789C98DC4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEF2FD8E-F80A-40EE-A006-EFAA52CFEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6C42ADF-9D19-4417-9A89-6832AE6459BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{59CF439D-C559-4B4A-B75E-B52EF0A99577}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{DBF6D6B9-186B-4166-894F-F42FA46C9F38}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E299A37C-20B6-4383-98AC-D1FD9DB1E817}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A212C64F-51A6-409B-A7F4-8476CE36914F}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0068B1A7-124C-42D7-A45A-FC597F7F2F51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38A10BA-BC6D-4010-8C5F-24F9E16C4A10}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9D909-A04F-4FD1-A0A6-CEACBAC939CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE761A-3115-4714-A172-BFC6E962DFB1}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -50109,7 +50109,7 @@
         <v>14</v>
       </c>
       <c r="R368" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S368" t="s">
         <v>897</v>
@@ -50168,7 +50168,7 @@
         <v>14</v>
       </c>
       <c r="R369" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S369" t="s">
         <v>897</v>
@@ -50463,7 +50463,7 @@
         <v>14</v>
       </c>
       <c r="R374" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S374" t="s">
         <v>897</v>
@@ -50522,7 +50522,7 @@
         <v>14</v>
       </c>
       <c r="R375" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S375" t="s">
         <v>897</v>
@@ -68861,7 +68861,7 @@
         <v>14</v>
       </c>
       <c r="R696" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S696" t="s">
         <v>897</v>
@@ -68911,7 +68911,7 @@
         <v>14</v>
       </c>
       <c r="R697" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S697" t="s">
         <v>897</v>
@@ -68961,7 +68961,7 @@
         <v>14</v>
       </c>
       <c r="R698" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S698" t="s">
         <v>897</v>
@@ -69011,7 +69011,7 @@
         <v>14</v>
       </c>
       <c r="R699" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S699" t="s">
         <v>897</v>
@@ -69379,7 +69379,7 @@
         <v>14</v>
       </c>
       <c r="R706" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S706" t="s">
         <v>897</v>
@@ -69438,7 +69438,7 @@
         <v>14</v>
       </c>
       <c r="R707" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S707" t="s">
         <v>897</v>
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FF158A-C6C6-4D01-8ED6-802789C98DC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8581600F-D658-4057-9975-8C3EDE34DDC3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6C42ADF-9D19-4417-9A89-6832AE6459BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BB4DD28-D7A8-46F1-9B50-4546BFCD2CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{DBF6D6B9-186B-4166-894F-F42FA46C9F38}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{192B2BE9-7EB9-4F6D-BD59-D87E54AAF5C6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A212C64F-51A6-409B-A7F4-8476CE36914F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B446B9C0-D884-487A-9F83-33E393518E91}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D38A10BA-BC6D-4010-8C5F-24F9E16C4A10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9F5FAD-515D-48AE-8CDA-AEC3E5AEB306}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE761A-3115-4714-A172-BFC6E962DFB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40784AD0-B70B-4C2A-856D-69AFE8D956EA}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -50109,7 +50109,7 @@
         <v>14</v>
       </c>
       <c r="R368" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S368" t="s">
         <v>897</v>
@@ -50168,7 +50168,7 @@
         <v>14</v>
       </c>
       <c r="R369" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S369" t="s">
         <v>897</v>
@@ -50463,7 +50463,7 @@
         <v>14</v>
       </c>
       <c r="R374" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S374" t="s">
         <v>897</v>
@@ -50522,7 +50522,7 @@
         <v>14</v>
       </c>
       <c r="R375" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S375" t="s">
         <v>897</v>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -66556,7 +66556,7 @@
         <v>14</v>
       </c>
       <c r="R652" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S652" t="s">
         <v>897</v>
@@ -66612,7 +66612,7 @@
         <v>14</v>
       </c>
       <c r="R653" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S653" t="s">
         <v>897</v>
@@ -67166,7 +67166,7 @@
         <v>14</v>
       </c>
       <c r="R663" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S663" t="s">
         <v>897</v>
@@ -67216,7 +67216,7 @@
         <v>14</v>
       </c>
       <c r="R664" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S664" t="s">
         <v>897</v>
@@ -68461,7 +68461,7 @@
         <v>14</v>
       </c>
       <c r="R688" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S688" t="s">
         <v>897</v>
@@ -68511,7 +68511,7 @@
         <v>14</v>
       </c>
       <c r="R689" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S689" t="s">
         <v>897</v>
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8581600F-D658-4057-9975-8C3EDE34DDC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E7718C-3FED-4E83-8127-9C95B6E2EBB3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BB4DD28-D7A8-46F1-9B50-4546BFCD2CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FEB4ED-D712-47A7-AA35-8C9510DC9B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{192B2BE9-7EB9-4F6D-BD59-D87E54AAF5C6}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{83A6875E-0D3A-4108-BE46-48E142BCDE5F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B446B9C0-D884-487A-9F83-33E393518E91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439EACFA-3A69-421C-92D0-86373E37F32E}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB9F5FAD-515D-48AE-8CDA-AEC3E5AEB306}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29D52B0-CBCA-4ECF-9B5E-B970AA9673C9}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40784AD0-B70B-4C2A-856D-69AFE8D956EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10028D27-CBD7-4F4C-8209-D5A660E9F91A}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -50109,7 +50109,7 @@
         <v>14</v>
       </c>
       <c r="R368" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S368" t="s">
         <v>897</v>
@@ -50168,7 +50168,7 @@
         <v>14</v>
       </c>
       <c r="R369" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S369" t="s">
         <v>897</v>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -66556,7 +66556,7 @@
         <v>14</v>
       </c>
       <c r="R652" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S652" t="s">
         <v>897</v>
@@ -66612,7 +66612,7 @@
         <v>14</v>
       </c>
       <c r="R653" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S653" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -67166,7 +67166,7 @@
         <v>14</v>
       </c>
       <c r="R663" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S663" t="s">
         <v>897</v>
@@ -67216,7 +67216,7 @@
         <v>14</v>
       </c>
       <c r="R664" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S664" t="s">
         <v>897</v>
@@ -68361,7 +68361,7 @@
         <v>14</v>
       </c>
       <c r="R686" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S686" t="s">
         <v>897</v>
@@ -68411,7 +68411,7 @@
         <v>14</v>
       </c>
       <c r="R687" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S687" t="s">
         <v>897</v>
@@ -69061,7 +69061,7 @@
         <v>14</v>
       </c>
       <c r="R700" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S700" t="s">
         <v>897</v>
@@ -69111,7 +69111,7 @@
         <v>14</v>
       </c>
       <c r="R701" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S701" t="s">
         <v>897</v>
@@ -69379,7 +69379,7 @@
         <v>14</v>
       </c>
       <c r="R706" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S706" t="s">
         <v>897</v>
@@ -69438,7 +69438,7 @@
         <v>14</v>
       </c>
       <c r="R707" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S707" t="s">
         <v>897</v>
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E7718C-3FED-4E83-8127-9C95B6E2EBB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DEE279-815E-4EE2-BA7A-5B09CB38FFF2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2FEB4ED-D712-47A7-AA35-8C9510DC9B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F0767CA-2B9F-43FF-868F-ED8820C41CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{83A6875E-0D3A-4108-BE46-48E142BCDE5F}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{61B916B2-3833-4157-BBA9-CA8FFE5F9103}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439EACFA-3A69-421C-92D0-86373E37F32E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F50FA54-69C7-42DE-AF3C-E5F0045152F8}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29D52B0-CBCA-4ECF-9B5E-B970AA9673C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B356AB6-B24D-4A49-A873-B3D6A965B7EA}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10028D27-CBD7-4F4C-8209-D5A660E9F91A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F0C8B8-00A5-47E2-8716-7CA47A6B6674}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -67166,7 +67166,7 @@
         <v>14</v>
       </c>
       <c r="R663" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S663" t="s">
         <v>897</v>
@@ -67216,7 +67216,7 @@
         <v>14</v>
       </c>
       <c r="R664" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S664" t="s">
         <v>897</v>
@@ -68361,7 +68361,7 @@
         <v>14</v>
       </c>
       <c r="R686" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S686" t="s">
         <v>897</v>
@@ -68411,7 +68411,7 @@
         <v>14</v>
       </c>
       <c r="R687" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S687" t="s">
         <v>897</v>
@@ -69061,7 +69061,7 @@
         <v>14</v>
       </c>
       <c r="R700" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S700" t="s">
         <v>897</v>
@@ -69111,7 +69111,7 @@
         <v>14</v>
       </c>
       <c r="R701" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S701" t="s">
         <v>897</v>
@@ -83449,7 +83449,7 @@
         <v>33</v>
       </c>
       <c r="M1081">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1082" spans="2:13" x14ac:dyDescent="0.25">
@@ -83478,7 +83478,7 @@
         <v>33</v>
       </c>
       <c r="M1082">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1083" spans="2:13" x14ac:dyDescent="0.25">
@@ -83507,7 +83507,7 @@
         <v>33</v>
       </c>
       <c r="M1083">
-        <v>0.4107492560960288</v>
+        <v>0.41074925609602891</v>
       </c>
     </row>
     <row r="1084" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DEE279-815E-4EE2-BA7A-5B09CB38FFF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15B747A-46EA-4C2D-B37E-CC16237B36D4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F0767CA-2B9F-43FF-868F-ED8820C41CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53CFCC9C-7FD9-4147-8694-6267259E2261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{61B916B2-3833-4157-BBA9-CA8FFE5F9103}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{2CF7199F-6B74-402A-A7CE-F74A8E11E6F5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F50FA54-69C7-42DE-AF3C-E5F0045152F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66064251-6674-4281-8E6C-E528A85264FA}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B356AB6-B24D-4A49-A873-B3D6A965B7EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B0D675-6DFA-4933-972F-305F50D7A32B}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F0C8B8-00A5-47E2-8716-7CA47A6B6674}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D72896-DE90-4334-9B11-B84A2CE082AC}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -50463,7 +50463,7 @@
         <v>14</v>
       </c>
       <c r="R374" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S374" t="s">
         <v>897</v>
@@ -50522,7 +50522,7 @@
         <v>14</v>
       </c>
       <c r="R375" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S375" t="s">
         <v>897</v>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -66556,7 +66556,7 @@
         <v>14</v>
       </c>
       <c r="R652" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S652" t="s">
         <v>897</v>
@@ -66612,7 +66612,7 @@
         <v>14</v>
       </c>
       <c r="R653" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S653" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -67166,7 +67166,7 @@
         <v>14</v>
       </c>
       <c r="R663" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S663" t="s">
         <v>897</v>
@@ -67216,7 +67216,7 @@
         <v>14</v>
       </c>
       <c r="R664" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S664" t="s">
         <v>897</v>
@@ -68861,7 +68861,7 @@
         <v>14</v>
       </c>
       <c r="R696" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S696" t="s">
         <v>897</v>
@@ -68911,7 +68911,7 @@
         <v>14</v>
       </c>
       <c r="R697" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S697" t="s">
         <v>897</v>
@@ -68961,7 +68961,7 @@
         <v>14</v>
       </c>
       <c r="R698" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S698" t="s">
         <v>897</v>
@@ -69011,7 +69011,7 @@
         <v>14</v>
       </c>
       <c r="R699" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S699" t="s">
         <v>897</v>
@@ -69061,7 +69061,7 @@
         <v>14</v>
       </c>
       <c r="R700" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S700" t="s">
         <v>897</v>
@@ -69111,7 +69111,7 @@
         <v>14</v>
       </c>
       <c r="R701" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S701" t="s">
         <v>897</v>
@@ -69379,7 +69379,7 @@
         <v>14</v>
       </c>
       <c r="R706" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S706" t="s">
         <v>897</v>
@@ -69438,7 +69438,7 @@
         <v>14</v>
       </c>
       <c r="R707" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S707" t="s">
         <v>897</v>
@@ -71848,7 +71848,7 @@
         <v>33</v>
       </c>
       <c r="M775">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="776" spans="2:13" x14ac:dyDescent="0.25">
@@ -71877,7 +71877,7 @@
         <v>33</v>
       </c>
       <c r="M776">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="777" spans="2:13" x14ac:dyDescent="0.25">
@@ -71906,7 +71906,7 @@
         <v>33</v>
       </c>
       <c r="M777">
-        <v>0.1823413782488186</v>
+        <v>0.18234137824881863</v>
       </c>
     </row>
     <row r="778" spans="2:13" x14ac:dyDescent="0.25">
@@ -83840,7 +83840,7 @@
         <v>33</v>
       </c>
       <c r="M1092">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1093" spans="2:13" x14ac:dyDescent="0.25">
@@ -83869,7 +83869,7 @@
         <v>33</v>
       </c>
       <c r="M1093">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1094" spans="2:13" x14ac:dyDescent="0.25">
@@ -83898,7 +83898,7 @@
         <v>33</v>
       </c>
       <c r="M1094">
-        <v>0.31020706828323896</v>
+        <v>0.31020706828323891</v>
       </c>
     </row>
     <row r="1095" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15B747A-46EA-4C2D-B37E-CC16237B36D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C372E6F-AC9E-422A-A5B3-223CF77AABA0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
+++ b/VerveStacks_JPN_grids_kan/vt_vervestacks_JPN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53CFCC9C-7FD9-4147-8694-6267259E2261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04983C53-DF79-4CDA-9814-ECBE58F04D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{2CF7199F-6B74-402A-A7CE-F74A8E11E6F5}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{361C36F8-205F-4A29-B545-0DA7BA8F0F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -6079,7 +6079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66064251-6674-4281-8E6C-E528A85264FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEB0BC9-DC37-4E31-8ADB-096644F3780A}">
   <dimension ref="B9:V264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -21907,7 +21907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B0D675-6DFA-4933-972F-305F50D7A32B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB4FB79-530E-4A1E-BDAC-9F24862663FF}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29171,7 +29171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D72896-DE90-4334-9B11-B84A2CE082AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D6325E-42E6-4EC7-BA54-8DCE634019B9}">
   <dimension ref="B9:V1220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -65548,7 +65548,7 @@
         <v>14</v>
       </c>
       <c r="R634" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S634" t="s">
         <v>897</v>
@@ -65604,7 +65604,7 @@
         <v>14</v>
       </c>
       <c r="R635" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S635" t="s">
         <v>897</v>
@@ -65660,7 +65660,7 @@
         <v>14</v>
       </c>
       <c r="R636" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S636" t="s">
         <v>897</v>
@@ -65716,7 +65716,7 @@
         <v>14</v>
       </c>
       <c r="R637" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S637" t="s">
         <v>897</v>
@@ -66724,7 +66724,7 @@
         <v>14</v>
       </c>
       <c r="R655" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S655" t="s">
         <v>897</v>
@@ -66780,7 +66780,7 @@
         <v>14</v>
       </c>
       <c r="R656" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S656" t="s">
         <v>897</v>
@@ -68461,7 +68461,7 @@
         <v>14</v>
       </c>
       <c r="R688" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S688" t="s">
         <v>897</v>
@@ -68511,7 +68511,7 @@
         <v>14</v>
       </c>
       <c r="R689" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S689" t="s">
         <v>897</v>
@@ -68961,7 +68961,7 @@
         <v>14</v>
       </c>
       <c r="R698" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="S698" t="s">
         <v>897</v>
@@ -69011,7 +69011,7 @@
         <v>14</v>
       </c>
       <c r="R699" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="S699" t="s">
         <v>897</v>
@@ -71848,7 +71848,7 @@
         <v>33</v>
       </c>
       <c r="M775">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="776" spans="2:13" x14ac:dyDescent="0.25">
@@ -71877,7 +71877,7 @@
         <v>33</v>
       </c>
       <c r="M776">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="777" spans="2:13" x14ac:dyDescent="0.25">
@@ -71906,7 +71906,7 @@
         <v>33</v>
       </c>
       <c r="M777">
-        <v>0.18234137824881863</v>
+        <v>0.1823413782488186</v>
       </c>
     </row>
     <row r="778" spans="2:13" x14ac:dyDescent="0.25">
@@ -83840,7 +83840,7 @@
         <v>33</v>
       </c>
       <c r="M1092">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1093" spans="2:13" x14ac:dyDescent="0.25">
@@ -83869,7 +83869,7 @@
         <v>33</v>
       </c>
       <c r="M1093">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1094" spans="2:13" x14ac:dyDescent="0.25">
@@ -83898,7 +83898,7 @@
         <v>33</v>
       </c>
       <c r="M1094">
-        <v>0.31020706828323891</v>
+        <v>0.31020706828323896</v>
       </c>
     </row>
     <row r="1095" spans="2:13" x14ac:dyDescent="0.25">
@@ -88695,7 +88695,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C372E6F-AC9E-422A-A5B3-223CF77AABA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2930BD4B-E13C-47CE-BCC2-2793EC01CC0A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
